--- a/exports/trend_1d/COLPAL_full_report.xlsx
+++ b/exports/trend_1d/COLPAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.51</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>937.78</v>
+        <v>919.53</v>
       </c>
       <c r="I2" t="n">
         <v>921.6992299999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.69</v>
+        <v>-5.56</v>
       </c>
       <c r="L2" t="n">
-        <v>4.21</v>
+        <v>6.03</v>
       </c>
       <c r="M2" t="n">
         <v>0.64</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
         <v>0.45</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42055</v>
+        <v>42058</v>
       </c>
       <c r="H3" t="n">
-        <v>960.4</v>
+        <v>986.6799999999999</v>
       </c>
       <c r="I3" t="n">
         <v>986.0568365931794</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.44</v>
+        <v>-7.3</v>
       </c>
       <c r="L3" t="n">
-        <v>5.76</v>
+        <v>7.62</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
         <v>-1.95</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>1006.45</v>
+        <v>990.9</v>
       </c>
       <c r="I4" t="n">
         <v>997.6839630423515</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
       <c r="L4" t="n">
         <v>3.51</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.02</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42184</v>
+        <v>42185</v>
       </c>
       <c r="H5" t="n">
-        <v>999.38</v>
+        <v>1019.88</v>
       </c>
       <c r="I5" t="n">
         <v>1014.261832119094</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.86</v>
+        <v>-2.92</v>
       </c>
       <c r="L5" t="n">
         <v>6.64</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>7.37</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>997.25</v>
+        <v>967.6799999999999</v>
       </c>
       <c r="I6" t="n">
         <v>986.2413958262965</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.22</v>
+        <v>-5.12</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>5.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N6" t="n">
         <v>3.6</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.26</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42261</v>
+        <v>42262</v>
       </c>
       <c r="H7" t="n">
-        <v>962.4</v>
+        <v>973.83</v>
       </c>
       <c r="I7" t="n">
         <v>971.9935441802836</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>0.55</v>
+        <v>-0.64</v>
       </c>
       <c r="L7" t="n">
         <v>2.68</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42290</v>
+        <v>42291</v>
       </c>
       <c r="H8" t="n">
-        <v>916.9</v>
+        <v>910</v>
       </c>
       <c r="I8" t="n">
         <v>913.0712231633159</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.85</v>
+        <v>-6.55</v>
       </c>
       <c r="L8" t="n">
-        <v>6.63</v>
+        <v>7.17</v>
       </c>
       <c r="M8" t="n">
         <v>2.08</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.66</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42304</v>
+        <v>42305</v>
       </c>
       <c r="H9" t="n">
-        <v>947.55</v>
+        <v>979.35</v>
       </c>
       <c r="I9" t="n">
         <v>969.9418449869744</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.13</v>
+        <v>-7.62</v>
       </c>
       <c r="L9" t="n">
-        <v>5.49</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
         <v>1.16</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.5</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H10" t="n">
-        <v>949.45</v>
+        <v>915.55</v>
       </c>
       <c r="I10" t="n">
         <v>941.3050006673251</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.05</v>
+        <v>-6.51</v>
       </c>
       <c r="L10" t="n">
-        <v>7.19</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
         <v>0.63</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.57</v>
       </c>
       <c r="O10" t="n">
         <v>3.36</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.3</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42520</v>
+        <v>42521</v>
       </c>
       <c r="H11" t="n">
-        <v>853.8</v>
+        <v>861.35</v>
       </c>
       <c r="I11" t="n">
         <v>854.4922453331509</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K11" t="n">
-        <v>6.74</v>
+        <v>5.92</v>
       </c>
       <c r="L11" t="n">
         <v>3.88</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.71</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42656</v>
+        <v>42657</v>
       </c>
       <c r="H12" t="n">
-        <v>932.7</v>
+        <v>920.45</v>
       </c>
       <c r="I12" t="n">
         <v>931.283181335669</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K12" t="n">
-        <v>8.279999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="L12" t="n">
         <v>1.61</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>7.6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H13" t="n">
-        <v>954.45</v>
+        <v>984.15</v>
       </c>
       <c r="I13" t="n">
         <v>978.4736253384306</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.69</v>
+        <v>-6.92</v>
       </c>
       <c r="L13" t="n">
-        <v>7.86</v>
+        <v>12.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.26</v>
+        <v>2.68</v>
       </c>
       <c r="N13" t="n">
         <v>3.95</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.85</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H14" t="n">
-        <v>949.05</v>
+        <v>914.8</v>
       </c>
       <c r="I14" t="n">
         <v>916.7522241450595</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.57</v>
+        <v>-7.05</v>
       </c>
       <c r="L14" t="n">
-        <v>8.630000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="M14" t="n">
         <v>6.31</v>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>3.61</v>
       </c>
       <c r="O14" t="n">
         <v>3.11</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.53</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42800</v>
+        <v>42801</v>
       </c>
       <c r="H15" t="n">
-        <v>909.75</v>
+        <v>927.3</v>
       </c>
       <c r="I15" t="n">
         <v>924.1471454610089</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K15" t="n">
-        <v>0.55</v>
+        <v>-1.37</v>
       </c>
       <c r="L15" t="n">
         <v>3.75</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>6.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42870</v>
+        <v>42871</v>
       </c>
       <c r="H16" t="n">
-        <v>994.35</v>
+        <v>976.6</v>
       </c>
       <c r="I16" t="n">
         <v>977.9247710459881</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>7.23</v>
+        <v>5.32</v>
       </c>
       <c r="L16" t="n">
         <v>2.16</v>
       </c>
       <c r="M16" t="n">
-        <v>1.39</v>
+        <v>2.46</v>
       </c>
       <c r="N16" t="n">
         <v>2.78</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42892</v>
+        <v>42893</v>
       </c>
       <c r="H17" t="n">
-        <v>1027.05</v>
+        <v>1066.1</v>
       </c>
       <c r="I17" t="n">
         <v>1049.283936926906</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.17</v>
+        <v>-9.16</v>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>3.88</v>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>-1.79</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42948</v>
+        <v>42949</v>
       </c>
       <c r="H18" t="n">
-        <v>1069.75</v>
+        <v>1039.25</v>
       </c>
       <c r="I18" t="n">
         <v>1054.292822329816</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K18" t="n">
-        <v>0.34</v>
+        <v>-2.52</v>
       </c>
       <c r="L18" t="n">
         <v>3.52</v>
@@ -1467,7 +1682,7 @@
         <v>1.21</v>
       </c>
       <c r="N18" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
         <v>3.8</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.28</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H19" t="n">
-        <v>1112.55</v>
+        <v>1124.25</v>
       </c>
       <c r="I19" t="n">
         <v>1114.941544771533</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.05</v>
+        <v>-8.18</v>
       </c>
       <c r="L19" t="n">
-        <v>7.67</v>
+        <v>9.02</v>
       </c>
       <c r="M19" t="n">
         <v>0.98</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.43</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H20" t="n">
-        <v>1100.75</v>
+        <v>1084.85</v>
       </c>
       <c r="I20" t="n">
         <v>1091.480291189692</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.09</v>
+        <v>-3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>2.69</v>
+        <v>3.94</v>
       </c>
       <c r="M20" t="n">
         <v>0.38</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H21" t="n">
-        <v>1083.3</v>
+        <v>1090.55</v>
       </c>
       <c r="I21" t="n">
         <v>1090.209980801764</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" t="n">
-        <v>0.14</v>
+        <v>-0.53</v>
       </c>
       <c r="L21" t="n">
         <v>3.79</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H22" t="n">
-        <v>1122.65</v>
+        <v>1100.2</v>
       </c>
       <c r="I22" t="n">
         <v>1101.510904072782</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K22" t="n">
-        <v>2.94</v>
+        <v>0.88</v>
       </c>
       <c r="L22" t="n">
         <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="N22" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>0.67</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.71</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43193</v>
+        <v>43194</v>
       </c>
       <c r="H23" t="n">
-        <v>1085</v>
+        <v>1091.4</v>
       </c>
       <c r="I23" t="n">
         <v>1091.085812801419</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>1.38</v>
+        <v>0.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.23</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.79</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43278</v>
+        <v>43279</v>
       </c>
       <c r="H24" t="n">
-        <v>1181.45</v>
+        <v>1155.55</v>
       </c>
       <c r="I24" t="n">
         <v>1162.951717721399</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K24" t="n">
-        <v>8.25</v>
+        <v>5.88</v>
       </c>
       <c r="L24" t="n">
         <v>1.31</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H25" t="n">
-        <v>1166.2</v>
+        <v>1191.6</v>
       </c>
       <c r="I25" t="n">
         <v>1170.927289072275</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.92</v>
+        <v>-3.12</v>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="M25" t="n">
         <v>1.68</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.39</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H26" t="n">
-        <v>1126.95</v>
+        <v>1096.8</v>
       </c>
       <c r="I26" t="n">
         <v>1115.468196771337</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.43</v>
+        <v>-7.96</v>
       </c>
       <c r="L26" t="n">
-        <v>5.59</v>
+        <v>8.33</v>
       </c>
       <c r="M26" t="n">
         <v>0.47</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O26" t="n">
         <v>2.18</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43395</v>
+        <v>43396</v>
       </c>
       <c r="H27" t="n">
-        <v>1124.75</v>
+        <v>1135.2</v>
       </c>
       <c r="I27" t="n">
         <v>1129.800342473183</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.55</v>
+        <v>-3.5</v>
       </c>
       <c r="L27" t="n">
         <v>4.85</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H28" t="n">
-        <v>1274.75</v>
+        <v>1249</v>
       </c>
       <c r="I28" t="n">
         <v>1255.6313197708</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K28" t="n">
-        <v>12.29</v>
+        <v>10.02</v>
       </c>
       <c r="L28" t="n">
         <v>4.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H29" t="n">
-        <v>1167.15</v>
+        <v>1203.65</v>
       </c>
       <c r="I29" t="n">
         <v>1183.501968591222</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K29" t="n">
-        <v>6.55</v>
+        <v>3.63</v>
       </c>
       <c r="L29" t="n">
         <v>4.76</v>
@@ -2094,7 +2441,7 @@
         <v>1.26</v>
       </c>
       <c r="N29" t="n">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="O29" t="n">
         <v>-2.02</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.34</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43798</v>
+        <v>43801</v>
       </c>
       <c r="H30" t="n">
-        <v>1474.2</v>
+        <v>1451.5</v>
       </c>
       <c r="I30" t="n">
         <v>1466.999537220566</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K30" t="n">
-        <v>22.48</v>
+        <v>20.59</v>
       </c>
       <c r="L30" t="n">
         <v>5.38</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43846</v>
+        <v>43847</v>
       </c>
       <c r="H31" t="n">
-        <v>1509.35</v>
+        <v>1509.95</v>
       </c>
       <c r="I31" t="n">
         <v>1509.48957568983</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.99</v>
+        <v>-4.03</v>
       </c>
       <c r="L31" t="n">
         <v>4.63</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.98</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H32" t="n">
-        <v>1484.1</v>
+        <v>1396</v>
       </c>
       <c r="I32" t="n">
         <v>1449.842642450239</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.71</v>
+        <v>-7.55</v>
       </c>
       <c r="L32" t="n">
-        <v>3.23</v>
+        <v>8.23</v>
       </c>
       <c r="M32" t="n">
         <v>0.22</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>5.94</v>
       </c>
       <c r="O32" t="n">
         <v>0.04</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.14</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H33" t="n">
-        <v>1249.9</v>
+        <v>1318.85</v>
       </c>
       <c r="I33" t="n">
         <v>1277.709738412826</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K33" t="n">
-        <v>10.47</v>
+        <v>5.53</v>
       </c>
       <c r="L33" t="n">
         <v>8.02</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>17.73</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43957</v>
+        <v>43958</v>
       </c>
       <c r="H34" t="n">
-        <v>1341.2</v>
+        <v>1300.9</v>
       </c>
       <c r="I34" t="n">
         <v>1324.918066116526</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K34" t="n">
-        <v>1.69</v>
+        <v>-1.36</v>
       </c>
       <c r="L34" t="n">
         <v>4.16</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>16.18</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44022</v>
+        <v>44025</v>
       </c>
       <c r="H35" t="n">
-        <v>1392.2</v>
+        <v>1432.15</v>
       </c>
       <c r="I35" t="n">
         <v>1429.162445195352</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.02</v>
+        <v>-10.09</v>
       </c>
       <c r="L35" t="n">
-        <v>9.779999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="M35" t="n">
         <v>1.81</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>7.88</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H36" t="n">
-        <v>1367.4</v>
+        <v>1341.65</v>
       </c>
       <c r="I36" t="n">
         <v>1353.428031321803</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.52</v>
+        <v>-6.32</v>
       </c>
       <c r="L36" t="n">
-        <v>6.21</v>
+        <v>7.68</v>
       </c>
       <c r="M36" t="n">
         <v>0.53</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>6.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44099</v>
+        <v>44102</v>
       </c>
       <c r="H37" t="n">
-        <v>1415.7</v>
+        <v>1440.9</v>
       </c>
       <c r="I37" t="n">
         <v>1433.97787916025</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.52</v>
+        <v>-7.4</v>
       </c>
       <c r="L37" t="n">
-        <v>5.84</v>
+        <v>7.92</v>
       </c>
       <c r="M37" t="n">
         <v>0.85</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H38" t="n">
-        <v>1562.2</v>
+        <v>1542.7</v>
       </c>
       <c r="I38" t="n">
         <v>1542.998144272067</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K38" t="n">
-        <v>8.42</v>
+        <v>7.07</v>
       </c>
       <c r="L38" t="n">
         <v>2.45</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44259</v>
+        <v>44260</v>
       </c>
       <c r="H39" t="n">
-        <v>1620.2</v>
+        <v>1633.9</v>
       </c>
       <c r="I39" t="n">
         <v>1627.695669350541</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.02</v>
+        <v>-5.91</v>
       </c>
       <c r="L39" t="n">
         <v>8.19</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.2</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H40" t="n">
-        <v>1553.85</v>
+        <v>1530.25</v>
       </c>
       <c r="I40" t="n">
         <v>1547.184505712844</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.9</v>
+        <v>-6.34</v>
       </c>
       <c r="L40" t="n">
-        <v>5.55</v>
+        <v>6.6</v>
       </c>
       <c r="M40" t="n">
         <v>0.87</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.33</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44328</v>
+        <v>44330</v>
       </c>
       <c r="H41" t="n">
-        <v>1529.4</v>
+        <v>1566.95</v>
       </c>
       <c r="I41" t="n">
         <v>1565.441294953549</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>0.06</v>
+        <v>-2.4</v>
       </c>
       <c r="L41" t="n">
         <v>5.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.98</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="H42" t="n">
-        <v>1792.35</v>
+        <v>1709.5</v>
       </c>
       <c r="I42" t="n">
         <v>1711.005721788535</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K42" t="n">
-        <v>14.38</v>
+        <v>9.1</v>
       </c>
       <c r="L42" t="n">
         <v>2.23</v>
@@ -2835,7 +3338,7 @@
         <v>0.35</v>
       </c>
       <c r="N42" t="n">
-        <v>1.78</v>
+        <v>4.62</v>
       </c>
       <c r="O42" t="n">
         <v>2.46</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44445</v>
+        <v>44446</v>
       </c>
       <c r="H43" t="n">
-        <v>1702.55</v>
+        <v>1731.25</v>
       </c>
       <c r="I43" t="n">
         <v>1728.949135036308</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>0.41</v>
+        <v>-1.27</v>
       </c>
       <c r="L43" t="n">
         <v>5.17</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44487</v>
+        <v>44488</v>
       </c>
       <c r="H44" t="n">
-        <v>1667.85</v>
+        <v>1636.05</v>
       </c>
       <c r="I44" t="n">
         <v>1643.001758439689</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.66</v>
+        <v>-5.5</v>
       </c>
       <c r="L44" t="n">
-        <v>4.32</v>
+        <v>5.72</v>
       </c>
       <c r="M44" t="n">
         <v>0.58</v>
       </c>
       <c r="N44" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O44" t="n">
         <v>1.69</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44629</v>
+        <v>44630</v>
       </c>
       <c r="H45" t="n">
-        <v>1449.05</v>
+        <v>1496.95</v>
       </c>
       <c r="I45" t="n">
         <v>1484.866818686378</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K45" t="n">
-        <v>11.43</v>
+        <v>8.5</v>
       </c>
       <c r="L45" t="n">
         <v>2.62</v>
       </c>
       <c r="M45" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>3.31</v>
       </c>
       <c r="O45" t="n">
         <v>-1.91</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6</v>
+      </c>
+      <c r="U45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H46" t="n">
-        <v>1544.4</v>
+        <v>1502.6</v>
       </c>
       <c r="I46" t="n">
         <v>1507.292384404839</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K46" t="n">
-        <v>3.17</v>
+        <v>0.38</v>
       </c>
       <c r="L46" t="n">
         <v>2.55</v>
@@ -3063,7 +3614,7 @@
         <v>1.36</v>
       </c>
       <c r="N46" t="n">
-        <v>1.41</v>
+        <v>2.71</v>
       </c>
       <c r="O46" t="n">
         <v>3.31</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.49</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44676</v>
+        <v>44677</v>
       </c>
       <c r="H47" t="n">
-        <v>1610.75</v>
+        <v>1625</v>
       </c>
       <c r="I47" t="n">
         <v>1613.844516103057</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.2</v>
+        <v>-8.15</v>
       </c>
       <c r="L47" t="n">
-        <v>8.109999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>0.5</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.98</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44715</v>
+        <v>44718</v>
       </c>
       <c r="H48" t="n">
-        <v>1562.8</v>
+        <v>1535.45</v>
       </c>
       <c r="I48" t="n">
         <v>1548.081519793408</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.83</v>
+        <v>-5.51</v>
       </c>
       <c r="L48" t="n">
-        <v>5.1</v>
+        <v>5.72</v>
       </c>
       <c r="M48" t="n">
         <v>1.06</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.74</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H49" t="n">
-        <v>1573.7</v>
+        <v>1606.35</v>
       </c>
       <c r="I49" t="n">
         <v>1576.696347286948</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.49</v>
+        <v>-4.62</v>
       </c>
       <c r="L49" t="n">
-        <v>3.29</v>
+        <v>4.86</v>
       </c>
       <c r="M49" t="n">
         <v>0.6899999999999999</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H50" t="n">
-        <v>1631.35</v>
+        <v>1563.25</v>
       </c>
       <c r="I50" t="n">
         <v>1577.536574412391</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K50" t="n">
-        <v>1.56</v>
+        <v>-2.68</v>
       </c>
       <c r="L50" t="n">
         <v>5.6</v>
@@ -3291,7 +3890,7 @@
         <v>1.31</v>
       </c>
       <c r="N50" t="n">
-        <v>2.54</v>
+        <v>4.17</v>
       </c>
       <c r="O50" t="n">
         <v>2.07</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H51" t="n">
-        <v>1636.8</v>
+        <v>1656.95</v>
       </c>
       <c r="I51" t="n">
         <v>1652.789067623301</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.7</v>
+        <v>-5.99</v>
       </c>
       <c r="L51" t="n">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M51" t="n">
         <v>1.11</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44909</v>
+        <v>44910</v>
       </c>
       <c r="H52" t="n">
-        <v>1571.5</v>
+        <v>1558.95</v>
       </c>
       <c r="I52" t="n">
         <v>1571.005288359909</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.16</v>
+        <v>-5.91</v>
       </c>
       <c r="L52" t="n">
-        <v>5.25</v>
+        <v>6.03</v>
       </c>
       <c r="M52" t="n">
         <v>0.13</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.59</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45007</v>
+        <v>45008</v>
       </c>
       <c r="H53" t="n">
-        <v>1504.5</v>
+        <v>1520.9</v>
       </c>
       <c r="I53" t="n">
         <v>1510.807767120811</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K53" t="n">
-        <v>3.49</v>
+        <v>2.44</v>
       </c>
       <c r="L53" t="n">
         <v>3.32</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.74</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H54" t="n">
-        <v>2689.6</v>
+        <v>2645.35</v>
       </c>
       <c r="I54" t="n">
         <v>2660.788855634692</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K54" t="n">
-        <v>76.84</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="L54" t="n">
         <v>2.03</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>292</v>
+        <v>293</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>15</v>
+      </c>
+      <c r="U54" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>7.78</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H55" t="n">
-        <v>2809.75</v>
+        <v>2960.05</v>
       </c>
       <c r="I55" t="n">
         <v>2828.977215635201</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.21</v>
+        <v>-11.9</v>
       </c>
       <c r="L55" t="n">
-        <v>6.56</v>
+        <v>16.02</v>
       </c>
       <c r="M55" t="n">
         <v>1.64</v>
       </c>
       <c r="N55" t="n">
-        <v>4.56</v>
+        <v>5.35</v>
       </c>
       <c r="O55" t="n">
         <v>-1.65</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45576</v>
+        <v>45579</v>
       </c>
       <c r="H56" t="n">
-        <v>3689.65</v>
+        <v>3522.45</v>
       </c>
       <c r="I56" t="n">
         <v>3568.703058517926</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K56" t="n">
-        <v>24.65</v>
+        <v>19</v>
       </c>
       <c r="L56" t="n">
         <v>5.9</v>
@@ -3633,7 +4304,7 @@
         <v>1.89</v>
       </c>
       <c r="N56" t="n">
-        <v>2.55</v>
+        <v>4.53</v>
       </c>
       <c r="O56" t="n">
         <v>5.35</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.63</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="H57" t="n">
-        <v>2834.55</v>
+        <v>2952.6</v>
       </c>
       <c r="I57" t="n">
         <v>2923.910566721406</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K57" t="n">
-        <v>19.53</v>
+        <v>16.18</v>
       </c>
       <c r="L57" t="n">
         <v>5.04</v>
@@ -3690,7 +4373,7 @@
         <v>1.27</v>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="O57" t="n">
         <v>-4.53</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.33</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="H58" t="n">
-        <v>2831.9</v>
+        <v>2774.35</v>
       </c>
       <c r="I58" t="n">
         <v>2786.702289674086</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.09</v>
+        <v>-6.04</v>
       </c>
       <c r="L58" t="n">
-        <v>5.93</v>
+        <v>6.18</v>
       </c>
       <c r="M58" t="n">
         <v>1.04</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H59" t="n">
-        <v>2789.75</v>
+        <v>2890.6</v>
       </c>
       <c r="I59" t="n">
         <v>2890.090461972341</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.19</v>
       </c>
       <c r="L59" t="n">
-        <v>2.13</v>
+        <v>5.95</v>
       </c>
       <c r="M59" t="n">
         <v>1.41</v>
       </c>
       <c r="N59" t="n">
-        <v>2.92</v>
+        <v>3.62</v>
       </c>
       <c r="O59" t="n">
         <v>-2.03</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="H60" t="n">
-        <v>2666.1</v>
+        <v>2612.2</v>
       </c>
       <c r="I60" t="n">
         <v>2624.375722023957</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K60" t="n">
-        <v>-7.77</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>9.699999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>1.1</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>11.04</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="H61" t="n">
-        <v>2513.7</v>
+        <v>2551.6</v>
       </c>
       <c r="I61" t="n">
         <v>2525.374721802873</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K61" t="n">
-        <v>3.77</v>
+        <v>2.32</v>
       </c>
       <c r="L61" t="n">
         <v>2.72</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.15</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="H62" t="n">
-        <v>2659.3</v>
+        <v>2487.1</v>
       </c>
       <c r="I62" t="n">
         <v>2504.674912068105</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K62" t="n">
-        <v>4.22</v>
+        <v>-2.53</v>
       </c>
       <c r="L62" t="n">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="M62" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="N62" t="n">
-        <v>3.2</v>
+        <v>6.48</v>
       </c>
       <c r="O62" t="n">
         <v>1.51</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>11.74</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H63" t="n">
-        <v>2273.5</v>
+        <v>2356.5</v>
       </c>
       <c r="I63" t="n">
         <v>2283.481351423702</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K63" t="n">
-        <v>8.59</v>
+        <v>5.25</v>
       </c>
       <c r="L63" t="n">
         <v>4.5</v>
@@ -4032,7 +4787,7 @@
         <v>2.14</v>
       </c>
       <c r="N63" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O63" t="n">
         <v>-6.48</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.32</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H64" t="n">
-        <v>2319</v>
+        <v>2274.2</v>
       </c>
       <c r="I64" t="n">
         <v>2289.307315397131</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.59</v>
+        <v>-3.49</v>
       </c>
       <c r="L64" t="n">
         <v>4.71</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.8</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H65" t="n">
-        <v>2104.8</v>
+        <v>2178</v>
       </c>
       <c r="I65" t="n">
         <v>2150.401559524612</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K65" t="n">
-        <v>7.45</v>
+        <v>4.23</v>
       </c>
       <c r="L65" t="n">
         <v>2.49</v>
@@ -4146,7 +4925,7 @@
         <v>0.75</v>
       </c>
       <c r="N65" t="n">
-        <v>2.64</v>
+        <v>3.48</v>
       </c>
       <c r="O65" t="n">
         <v>-1.93</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="H66" t="n">
-        <v>2198.3</v>
+        <v>2055.6</v>
       </c>
       <c r="I66" t="n">
         <v>2147.244364875749</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K66" t="n">
-        <v>0.93</v>
+        <v>-5.62</v>
       </c>
       <c r="L66" t="n">
         <v>6.82</v>
@@ -4203,7 +4994,7 @@
         <v>2.47</v>
       </c>
       <c r="N66" t="n">
-        <v>2.94</v>
+        <v>6.49</v>
       </c>
       <c r="O66" t="n">
         <v>3.48</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>11.6</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H67" t="n">
-        <v>1946.7</v>
+        <v>1977.4</v>
       </c>
       <c r="I67" t="n">
         <v>1975.565754494263</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K67" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="L67" t="n">
         <v>6.94</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.33</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H68" t="n">
-        <v>2059.9</v>
+        <v>1990.1</v>
       </c>
       <c r="I68" t="n">
         <v>2034.38123036507</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K68" t="n">
-        <v>4.17</v>
+        <v>0.64</v>
       </c>
       <c r="L68" t="n">
         <v>1.89</v>
@@ -4317,7 +5132,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N68" t="n">
-        <v>2.78</v>
+        <v>3.39</v>
       </c>
       <c r="O68" t="n">
         <v>1.58</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="H69" t="n">
-        <v>2086.1</v>
+        <v>2136.6</v>
       </c>
       <c r="I69" t="n">
         <v>2114.870899903002</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.82</v>
+        <v>-7.36</v>
       </c>
       <c r="L69" t="n">
-        <v>7.36</v>
+        <v>8.34</v>
       </c>
       <c r="M69" t="n">
         <v>1.01</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>7.55</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H70" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="I70" t="n">
         <v>2006.298117556085</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.02</v>
+        <v>-6.16</v>
       </c>
       <c r="L70" t="n">
-        <v>6.44</v>
+        <v>6.67</v>
       </c>
       <c r="M70" t="n">
         <v>0.12</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.23</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H71" t="n">
-        <v>1840.3</v>
+        <v>1917.8</v>
       </c>
       <c r="I71" t="n">
         <v>1893.810142571206</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K71" t="n">
-        <v>8.210000000000001</v>
+        <v>4.35</v>
       </c>
       <c r="L71" t="n">
         <v>0.15</v>
@@ -4488,7 +5339,7 @@
         <v>0.75</v>
       </c>
       <c r="N71" t="n">
-        <v>3.87</v>
+        <v>4.21</v>
       </c>
       <c r="O71" t="n">
         <v>-0.15</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H72" t="n">
-        <v>1763.3</v>
+        <v>1735</v>
       </c>
       <c r="I72" t="n">
         <v>1757.121604913129</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K72" t="n">
-        <v>-8.06</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>8.06</v>
+        <v>10.52</v>
       </c>
       <c r="M72" t="n">
         <v>1.33</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>18</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.8</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.04</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.52</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.52</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76.84</v>
+        <v>73.93000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.8</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.76</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.779999999999999</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="25">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.06</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="27">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
